--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T12:26:06+00:00</t>
+    <t>2024-07-08T12:27:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T12:27:07+00:00</t>
+    <t>2024-07-08T12:36:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T12:36:45+00:00</t>
+    <t>2024-07-08T13:09:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T13:09:52+00:00</t>
+    <t>2024-07-10T12:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:03:37+00:00</t>
+    <t>2024-07-10T12:30:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:30:30+00:00</t>
+    <t>2024-07-12T15:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T15:20:37+00:00</t>
+    <t>2024-07-12T15:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T15:47:39+00:00</t>
+    <t>2024-07-12T16:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T16:48:03+00:00</t>
+    <t>2024-07-12T17:10:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T17:10:54+00:00</t>
+    <t>2024-07-12T18:22:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T18:22:27+00:00</t>
+    <t>2024-07-12T19:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T19:35:04+00:00</t>
+    <t>2024-07-12T19:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T19:43:36+00:00</t>
+    <t>2024-07-13T07:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T07:40:27+00:00</t>
+    <t>2024-07-13T07:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T07:56:12+00:00</t>
+    <t>2024-07-13T08:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T08:57:57+00:00</t>
+    <t>2024-07-13T11:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T11:05:38+00:00</t>
+    <t>2024-07-13T11:14:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/feature/embed-examples/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T11:14:58+00:00</t>
+    <t>2024-07-13T14:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
